--- a/Oversigt over kontrakter på Spor Strøm forst og Sikring.xlsx
+++ b/Oversigt over kontrakter på Spor Strøm forst og Sikring.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stineskov/Desktop/Stineprojekt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B955A215-54A7-2440-898D-CF5F5D4B678E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DC8821-E181-E94A-9EA3-4DFAAF16C833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="680" windowWidth="30240" windowHeight="17440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Strøm og Materiel" sheetId="6" r:id="rId1"/>
     <sheet name="Sikring" sheetId="7" r:id="rId2"/>
     <sheet name="Beredskab (interne krav)" sheetId="8" r:id="rId3"/>
     <sheet name="Fors, afvanding geoteknik, bro" sheetId="9" r:id="rId4"/>
+    <sheet name="Oversigt over kontrakter" sheetId="10" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3679" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3902" uniqueCount="490">
   <si>
     <t>Vedligeholdelsesforvalter</t>
   </si>
@@ -1499,12 +1500,326 @@
   <si>
     <t>Indkøb af etablering og vedligeholdelse af Hegn - Øst</t>
   </si>
+  <si>
+    <t>Vedligeholdsesforvalter</t>
+  </si>
+  <si>
+    <t>Tommas Liebach Nielsen (TLNI)</t>
+  </si>
+  <si>
+    <t>Rene Bøge Jensen (RBOJ)</t>
+  </si>
+  <si>
+    <t>Benjamin Wagner Frederiksen (BWFR)</t>
+  </si>
+  <si>
+    <t>Rune Birch Hansen (RBHA)</t>
+  </si>
+  <si>
+    <t>Kim Snevig de Ridder (KSRD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bravida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB-ELCO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eltel </t>
+  </si>
+  <si>
+    <t>TK Elevator</t>
+  </si>
+  <si>
+    <t>Geografisk område + Banenumre / TIB strækning med responstid for enkelt strækning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nord- og midtjylland
+• Banenummer 24: Aarhus H - Langå
+• Banenummer 25: Aalborg - Frederikshavn
+• Banenummer 33a: Herning - Holstebro 
+• Banenummer 33b: Holstebro - Struer 
+• Banenummer 34: Struer - Thisted
+• Banenummer 52: Aalborg Lufthavn
+• Banenummer 55: Herning - Skanderborg 
+• Banenummer 71: Langå - Aalborg
+• Banenummer 92: Skjern - Holstebro 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydjylland og Fyn
+• Banenummer 15a: Nyborg - Odense
+• Banenummer 15b: Odense
+• Banenummer 16: Odense - Fredericia
+• Banenummer 23a: Fredericia - Vejle
+• Banenummer 23b: Vejle - (Skanderborg)
+• Banenummer 26: Fredericia - Padborg
+• Banenummer 27: Snoghøj - Taulov
+• Banenummer 28: Sønderborg - Tinglev 
+• Banenummer 29: Bramming - Lunderskov 
+• Banenummer 39: Vejle - (Herning)  
+• Banenummer 56: (Skjern) - (Herning)
+• Banenummer 78: Svendborg - Odense
+• Banenummer 90: Esbjerg - Varde
+• Banenummer 91: Varde - (Skjern)
+• Banenummer 94: Ribe - Bramming 
+• Banenummer 95: Ribe - Tønder
+• Banenummer 97: Esbjerg - Bramming
+• Banenummer 98: Rødekro - Vojens
+• Banenummer 99: Tinglev - Padborg
+</t>
+  </si>
+  <si>
+    <r>
+      <t>Hovedstaden
+• Banenummer 10: København H - Helsingør
+• Banenummer 11a: København H - Høje Taastrup
+• Banenummer 19: København H - Hvidovre Fjern
+• Banenummer 20: Ringsted - København H
+• Banenummer 70: Lersøen - Østerpost
+•</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Banenummer 80: Valby - Svanemøllen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+• Banenummer 82: Svanemøllen -Hillerød                                                                                                                      
+• Banenummer 83: Valby -Frederikssund                                                                                                                       
+• Banenummer 84: Svanemøllen - Farum                                                                                                                 
+• Banenummer 85: København H-Køge                                                                                                                      
+• Banenummer 86: Hellerup-Klampenborg
+• Banenummer 87: København Syd - Ryparken
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">Sjælland
+• Banenummer 11b: Roskilde - Høje Taastrup 
+• Banenummer 12: Ringsted - Roskilde
+• Banenummer 13: Ringsted - Korsør
+• Banenummer 21: Næstved - Nykøbing Falster
+• Banenummer 22: Nykøbing Falster - Rødby Færge  
+• Banenummer 40: Næstved - Roskilde 
+• Banenummer 50: Købemhavm H - Københavns Lufthavn
+• Banenummer 51: Kalundborg - Holbæk
+• Banenummer 79: Holbæk - Roskilde
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+  </si>
+  <si>
+    <t>Elektrificerede strækninger øst for Storebælt Strækning 
+• TIB 1
+• TIB 2: Ringsted - Rødby F.
+• TIB 4: Roskilde - Næstved
+• TIB 5: Roskilde - Kalundborg
+• TIB 7:
+• TIB 10: København H - Helsingør
+• TIB 81: København H-Høje Taastrup 
+• TIB 82: København H-Hillerød                                                                                                                       
+• TIB 83: Valby -Frederikssund                                                                                                                        
+• TIB 84: Svanemøllen -Farum                                                                                                                  
+• TIB 85: København H-Køge                                                                                                                       
+• TIB 86: Hellerup-Klampenborg                                                                                                
+• TIB 88: København Syd-Hellerup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elektrificerede strækninger vest for Storebælt Strækning
+• TIB 22:
+• TIB 23:  
+• TIB 26: Fredericia - Padborg
+• TIB 27:
+• TIB 28: Sønderborg - Tinglev
+• TIB 29: Lunderskov - Esbjerg    
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elektrificerede strækninger på Fjernbanen
+TIB 1:
+TIB 2:
+TIB 4:
+TIB 10:
+TIB 21
+TIB 22:
+TIB 26:
+TIB 28:
+TIB 29:
+TIB 79
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sjælland
+S-Banen. Strækning 80 til 88
+• TIB 81: København H-Høje Taastrup 
+• TIB 82: København H-Hillerød                                                                                                                       
+• TIB 83: Valby -Frederikssund                                                                                                                        
+• TIB 84: Svanemøllen -Farum                                                                                                                  
+• TIB 85: København H-Køge                                                                                                                       
+• TIB 86: Hellerup-Klampenborg                                                                                                
+• TIB 88: København Syd-Hellerup
+</t>
+  </si>
+  <si>
+    <t>Sjælland
+S-Banen. Strækning 80 til 88
+• TIB 81: København H-Høje Taastrup 
+• TIB 82: København H-Hillerød                                                                                                                       
+• TIB 83: Valby -Frederikssund                                                                                                                        
+• TIB 84: Svanemøllen -Farum                                                                                                                  
+• TIB 85: København H-Køge                                                                                                                       
+• TIB 86: Hellerup-Klampenborg                                                                                               
+• TIB 88: København Syd-Hellerup</t>
+  </si>
+  <si>
+    <t>Landsdækkende 
+• TIB 1: 
+• TIB 2: Ringsted - Rødby F
+• TIB 5: 
+• TIB 10: København H - Helsingør 
+• TIB 23: Fredericia - Aarhus H
+• TIB 26: Fredericia - Padborg</t>
+  </si>
+  <si>
+    <t>TIB 1</t>
+  </si>
+  <si>
+    <t>Varighed i år (inkl. mobilisering + option på forlængelse)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Entreprenøren skal etablere et beredskab bestående af køretøjer, særligt værktøj samt mandskab, som er </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>tilgængeligt i alle døgnets 24 timer i alle ugens 7 dage,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Beredskabet skal være klar til udrykning inden for responstiden og skal opretholdes i hele kontraktperioden. Medarbejdere der udfører fejlretning skal som minimum have to års dokumenteret erfaring, Pas på, på banen, arbejde i sikringshytter, og på strækninger med kørestrøm på S-banen eller fjernbane (S-banen SKI, Strækninger og stationer med kørestrøm fjernbane anlæg type 160 FKI.)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Entreprenøren skal etablere et beredskab bestående af køretøjer, særligt værktøj samt mandskab, som er</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tilgængeligt i alle døgnets 24 timer i alle ugens 7 dage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Beredskabet skal være klar til udrykning inden for responstiden og skal opretholdes i hele kontraktperioden. Medarbejdere der udfører fejlretning skal som minimum have to års dokumenteret erfaring, Pas på, på banen, arbejde i sikringshytter, og på strækninger med kørestrøm på S-banen eller fjernbane (S-banen SKI, Strækninger og stationer med kørestrøm fjernbane anlæg type 160 FKI.)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Beskrivelse af beredskabet </t>
+  </si>
+  <si>
+    <t>Antal fejl, som leverandøren skal kunne håndtere på én gang</t>
+  </si>
+  <si>
+    <t>Antal arbejdshold og personer pr. hold som leverandøren har pligt til at stille med</t>
+  </si>
+  <si>
+    <t>Henvisning til hvor det er beskrevet i kontrakten2</t>
+  </si>
+  <si>
+    <t>Ved større fejlretninger skal leverandør rapportere løbende status til BDK GFS, og hvis dette ikke er muligt til BDK fejlretningskoordinator.
+Der kan benyttes følgende metoder til håndtering af fejl: Endelig afhjælpning eller midlertidig afhjælpning.
+FKO/Vagthavende modtager fejlmelding og opretter fejlretningsnummer. Leverandørs fejlretningspersonale tilkaldes per telefon (start på responstid), og FKO/vagthavende registrerer tidspunkt for udkald. Fejlretningspersonale ankommer og meddeler til fejlretningskoordinator/vagthavende, der noterer ankomsttidspunkt (slut på responstid/start på fejlretningstid). Afhjælpningsforløb aftales mellem FKO/vagthavende og fejlretningspersonale. Hvis fejlretning kræver sporspærring og/eller kørestrømsafbrydelse etableres dette efter regnerle i SR og ORF/ORS. Al kommunikation om fejlretningsstatus skal gå via FKO/vagthavende. Fejlretningspersonale meddeler når fejl er afhjulpet, og FKO/vagthavende noterer tidspunktet i SAP (slut på fejlrentingstid). Eventuel sporspærring/kørestrømsafbrydelse ophæves efter aftale med FKO/vagthavende. Fejlretningspersonale skal sammen med FKO/vagthavende aftale på hvilke betingelser anlægget kan befares og evt. overvåges. Leverandør skal efterfølgende underrette den driftsansvarlige, hvis der er lagt restriktioner for anlægget.
+Leverandørens fejlretningspersonale afrapporterer fejlretningsforløb til BDK via SAP/app på vedligeholdelsesordren. Hvis fejlen er midlertidigt afhjulpet skal entreprenøren meddele  dette til GFS, og den endelige udbedring bestilles af GFS.</t>
+  </si>
+  <si>
+    <t>Afrapporteringsfrekvens leverandør</t>
+  </si>
+  <si>
+    <t>SE FIGUR 2</t>
+  </si>
+  <si>
+    <t>Peter Slag Rasmussen (PSRA)
+Gerhard Jensen (GEHE)</t>
+  </si>
+  <si>
+    <t>Christian Rønne Pedersen (CRPE)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fra 45 min. og op til 2 timer afhængig af adr/anlæg 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">SE FIGUR 1 </t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1538,8 +1853,84 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1570,8 +1961,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1594,11 +1991,163 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1648,18 +2197,198 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="99">
+  <dxfs count="123">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
+        <sz val="11"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -1672,10 +2401,598 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="9" tint="-0.499984740745262"/>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2248,80 +3565,12 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -2334,170 +3583,10 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="5"/>
+          <bgColor theme="9" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2517,130 +3606,404 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>526508</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2086934</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>368229</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>2184399</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Billede 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09EEB565-FB91-644B-9140-2E06B587644F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="43317041" y="3170667"/>
+          <a:ext cx="5649855" cy="2434265"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>321733</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>3132666</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>626532</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>2635113</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Billede 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9612EA1-BE3E-5847-AA1A-AB2B7BE28467}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="43112266" y="6553199"/>
+          <a:ext cx="6112933" cy="4717914"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>812800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1185334</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>423334</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1981201</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75C73877-10F0-423F-AB6C-053D3EA03E87}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44433067" y="2269067"/>
+          <a:ext cx="3759200" cy="795867"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="2800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FIGUR 1</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>84667</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>2387600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>524934</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>3183467</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1540BF5B-0622-924A-92AB-72395C15FB85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44534667" y="5808133"/>
+          <a:ext cx="3759200" cy="795867"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="2800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FIGUR 2</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{EF2102AC-8B6F-A940-A70C-5383A6E516E8}" name="Table5" displayName="Table5" ref="A1:AC100" totalsRowShown="0" headerRowDxfId="86" dataDxfId="85">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{EF2102AC-8B6F-A940-A70C-5383A6E516E8}" name="Table5" displayName="Table5" ref="A1:AC100" totalsRowShown="0" headerRowDxfId="91" dataDxfId="90">
   <autoFilter ref="A1:AC100" xr:uid="{EF2102AC-8B6F-A940-A70C-5383A6E516E8}"/>
   <tableColumns count="29">
-    <tableColumn id="1" xr3:uid="{67F96958-20A8-6148-AFBF-44CB63BF61A9}" name="Vedligeholdelsesforvalter" dataDxfId="84"/>
-    <tableColumn id="2" xr3:uid="{A85A38E6-18F5-D34E-B003-1E259E12CB7C}" name="Vedligeholdelsesforvalter - Initialer" dataDxfId="83"/>
-    <tableColumn id="3" xr3:uid="{024AD559-E801-B544-857D-E8A77F2053B6}" name="SAP nummer" dataDxfId="82"/>
-    <tableColumn id="4" xr3:uid="{7C3F03DB-AE86-2F45-9215-2DFE2BA295C0}" name="Kontraktens titel" dataDxfId="81"/>
-    <tableColumn id="5" xr3:uid="{E2975C02-0DDD-8543-8273-1A9C1B0E957D}" name="Leverandørnavn" dataDxfId="80"/>
-    <tableColumn id="6" xr3:uid="{96351597-F24D-9A4C-99B3-042A24DF6AF6}" name="Geografisk område" dataDxfId="79"/>
-    <tableColumn id="7" xr3:uid="{CA8F8803-B156-B043-8FE0-AD8AD90E65D4}" name="Områdebeskrivelse" dataDxfId="78"/>
-    <tableColumn id="8" xr3:uid="{F6D6EC48-75FD-6B40-8FE5-3B79517AAAB7}" name="Banenr. / TIB" dataDxfId="77"/>
-    <tableColumn id="9" xr3:uid="{844ADE35-2294-F249-8796-846239B3429F}" name="Strækningsnummer" dataDxfId="76"/>
-    <tableColumn id="10" xr3:uid="{0775402C-53FC-8C46-986D-21D4BE8D48A3}" name="Fra" dataDxfId="75"/>
-    <tableColumn id="11" xr3:uid="{7CEC438A-DCC0-5746-953F-A0D184F6B642}" name="Til" dataDxfId="74"/>
-    <tableColumn id="12" xr3:uid="{C2D6FE88-1D37-544A-B5B1-030B57866555}" name="Strækningsbeskrivelse" dataDxfId="73"/>
-    <tableColumn id="13" xr3:uid="{1A1859DD-BD79-E14E-9AC2-7C9B0DE82AD3}" name="Ikraft-trædelse" dataDxfId="72"/>
-    <tableColumn id="14" xr3:uid="{90F962F7-1ADD-BC48-84EE-8F0E3FA194D9}" name="Varighed _x000a_i år (inkl mobilisering + option på forlængelse)" dataDxfId="71"/>
-    <tableColumn id="15" xr3:uid="{140C0B35-FCF3-5648-9B4B-58EEEC5D2D8E}" name="Oversigt over bodsbelagte emner" dataDxfId="70"/>
-    <tableColumn id="16" xr3:uid="{99D9F053-52B2-B94C-92CE-6C89A27D5479}" name="Beskrivelse af og i givet fald hvordan bod/boderne maksimeres" dataDxfId="69"/>
-    <tableColumn id="17" xr3:uid="{1329127D-4EBD-1940-A810-A6CBE8381487}" name="Henvisning til hvor det er beskrevet i kontrakten" dataDxfId="68"/>
-    <tableColumn id="18" xr3:uid="{AA56E970-12AF-AC43-9C2E-C654E9490015}" name="Beskrivelse af beredskabet" dataDxfId="67"/>
-    <tableColumn id="19" xr3:uid="{22E0B878-4A77-4C4B-BDB0-BBBB16DDC8D7}" name="Antal fejl, som leverandøren skal kunne håndtere på én gang." dataDxfId="66"/>
-    <tableColumn id="20" xr3:uid="{CC6F5889-34C0-4B4A-9AEC-330123B7E649}" name="Antal arbejdshold og personer pr. hold, som leverandøren har pligt til at stille med." dataDxfId="65"/>
-    <tableColumn id="21" xr3:uid="{8C9BB7E1-3114-8E4E-B3FC-1836F9B25DBE}" name="Responstid" dataDxfId="64"/>
-    <tableColumn id="22" xr3:uid="{B39DC5C4-6A10-764D-A108-BC6BC47E2D73}" name="Beskrivelse af boderne" dataDxfId="63"/>
-    <tableColumn id="23" xr3:uid="{8A596402-55E4-D042-A827-D5CDF72400CA}" name="Henvisning til hvor der er beskrevet i kontrakten2" dataDxfId="62"/>
-    <tableColumn id="24" xr3:uid="{B5292259-DF23-E84C-9EB0-F38FAB7964FF}" name="Krav til data registrering" dataDxfId="61"/>
-    <tableColumn id="25" xr3:uid="{782933D1-BFB3-6542-982A-E83AEBA13D05}" name="Beskrevet fremgangsmåde omkring fejlretning" dataDxfId="60"/>
-    <tableColumn id="26" xr3:uid="{08FEF57A-AB7F-304F-AB33-58252440F44D}" name="Afrapporteringsfrekvens for leverandør" dataDxfId="59"/>
-    <tableColumn id="27" xr3:uid="{CB794F20-DEA0-554C-A15E-B545D6014A30}" name="GFS" dataDxfId="58"/>
-    <tableColumn id="28" xr3:uid="{CF3E5407-AAB4-C848-94BB-E7FF13108F7B}" name="Kontraktansvarlig (leder)" dataDxfId="57"/>
-    <tableColumn id="29" xr3:uid="{572378DA-2216-9D4A-9D9E-E5E3724DDC61}" name="Definitioner " dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{67F96958-20A8-6148-AFBF-44CB63BF61A9}" name="Vedligeholdelsesforvalter" dataDxfId="89"/>
+    <tableColumn id="2" xr3:uid="{A85A38E6-18F5-D34E-B003-1E259E12CB7C}" name="Vedligeholdelsesforvalter - Initialer" dataDxfId="88"/>
+    <tableColumn id="3" xr3:uid="{024AD559-E801-B544-857D-E8A77F2053B6}" name="SAP nummer" dataDxfId="87"/>
+    <tableColumn id="4" xr3:uid="{7C3F03DB-AE86-2F45-9215-2DFE2BA295C0}" name="Kontraktens titel" dataDxfId="86"/>
+    <tableColumn id="5" xr3:uid="{E2975C02-0DDD-8543-8273-1A9C1B0E957D}" name="Leverandørnavn" dataDxfId="85"/>
+    <tableColumn id="6" xr3:uid="{96351597-F24D-9A4C-99B3-042A24DF6AF6}" name="Geografisk område" dataDxfId="84"/>
+    <tableColumn id="7" xr3:uid="{CA8F8803-B156-B043-8FE0-AD8AD90E65D4}" name="Områdebeskrivelse" dataDxfId="83"/>
+    <tableColumn id="8" xr3:uid="{F6D6EC48-75FD-6B40-8FE5-3B79517AAAB7}" name="Banenr. / TIB" dataDxfId="82"/>
+    <tableColumn id="9" xr3:uid="{844ADE35-2294-F249-8796-846239B3429F}" name="Strækningsnummer" dataDxfId="81"/>
+    <tableColumn id="10" xr3:uid="{0775402C-53FC-8C46-986D-21D4BE8D48A3}" name="Fra" dataDxfId="80"/>
+    <tableColumn id="11" xr3:uid="{7CEC438A-DCC0-5746-953F-A0D184F6B642}" name="Til" dataDxfId="79"/>
+    <tableColumn id="12" xr3:uid="{C2D6FE88-1D37-544A-B5B1-030B57866555}" name="Strækningsbeskrivelse" dataDxfId="78"/>
+    <tableColumn id="13" xr3:uid="{1A1859DD-BD79-E14E-9AC2-7C9B0DE82AD3}" name="Ikraft-trædelse" dataDxfId="77"/>
+    <tableColumn id="14" xr3:uid="{90F962F7-1ADD-BC48-84EE-8F0E3FA194D9}" name="Varighed _x000a_i år (inkl mobilisering + option på forlængelse)" dataDxfId="76"/>
+    <tableColumn id="15" xr3:uid="{140C0B35-FCF3-5648-9B4B-58EEEC5D2D8E}" name="Oversigt over bodsbelagte emner" dataDxfId="75"/>
+    <tableColumn id="16" xr3:uid="{99D9F053-52B2-B94C-92CE-6C89A27D5479}" name="Beskrivelse af og i givet fald hvordan bod/boderne maksimeres" dataDxfId="74"/>
+    <tableColumn id="17" xr3:uid="{1329127D-4EBD-1940-A810-A6CBE8381487}" name="Henvisning til hvor det er beskrevet i kontrakten" dataDxfId="73"/>
+    <tableColumn id="18" xr3:uid="{AA56E970-12AF-AC43-9C2E-C654E9490015}" name="Beskrivelse af beredskabet" dataDxfId="72"/>
+    <tableColumn id="19" xr3:uid="{22E0B878-4A77-4C4B-BDB0-BBBB16DDC8D7}" name="Antal fejl, som leverandøren skal kunne håndtere på én gang." dataDxfId="71"/>
+    <tableColumn id="20" xr3:uid="{CC6F5889-34C0-4B4A-9AEC-330123B7E649}" name="Antal arbejdshold og personer pr. hold, som leverandøren har pligt til at stille med." dataDxfId="70"/>
+    <tableColumn id="21" xr3:uid="{8C9BB7E1-3114-8E4E-B3FC-1836F9B25DBE}" name="Responstid" dataDxfId="69"/>
+    <tableColumn id="22" xr3:uid="{B39DC5C4-6A10-764D-A108-BC6BC47E2D73}" name="Beskrivelse af boderne" dataDxfId="68"/>
+    <tableColumn id="23" xr3:uid="{8A596402-55E4-D042-A827-D5CDF72400CA}" name="Henvisning til hvor der er beskrevet i kontrakten2" dataDxfId="67"/>
+    <tableColumn id="24" xr3:uid="{B5292259-DF23-E84C-9EB0-F38FAB7964FF}" name="Krav til data registrering" dataDxfId="66"/>
+    <tableColumn id="25" xr3:uid="{782933D1-BFB3-6542-982A-E83AEBA13D05}" name="Beskrevet fremgangsmåde omkring fejlretning" dataDxfId="65"/>
+    <tableColumn id="26" xr3:uid="{08FEF57A-AB7F-304F-AB33-58252440F44D}" name="Afrapporteringsfrekvens for leverandør" dataDxfId="64"/>
+    <tableColumn id="27" xr3:uid="{CB794F20-DEA0-554C-A15E-B545D6014A30}" name="GFS" dataDxfId="63"/>
+    <tableColumn id="28" xr3:uid="{CF3E5407-AAB4-C848-94BB-E7FF13108F7B}" name="Kontraktansvarlig (leder)" dataDxfId="62"/>
+    <tableColumn id="29" xr3:uid="{572378DA-2216-9D4A-9D9E-E5E3724DDC61}" name="Definitioner " dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{51ACCBB3-7B85-5841-A5E2-CEBAD7DD14BB}" name="Table7" displayName="Table7" ref="A1:W12" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{51ACCBB3-7B85-5841-A5E2-CEBAD7DD14BB}" name="Table7" displayName="Table7" ref="A1:W12" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
   <autoFilter ref="A1:W12" xr:uid="{51ACCBB3-7B85-5841-A5E2-CEBAD7DD14BB}"/>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{E619BD56-AE44-6E4E-8101-8116FAEFB42E}" name="Vedligeholdelsesforvalter" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{87A87DF0-814D-8D43-9129-4149CCF7622A}" name="SAP nummer" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{776EFCC3-20CB-9E4F-9740-1B00141C6B81}" name="Kontraktens titel" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{F6B1E8AC-E32C-8A47-BE7D-89927CA6D80E}" name="Leverandørnavn" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{2DBCDBCE-42CF-014F-B910-157DC783157C}" name="Geografisk område + Banenumre/TIB-strækning med responstid for den enkelte strækning" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{C11B38E0-A6FD-8D47-A62E-0E2EFEBC6C6D}" name="Ikraft-trædelse" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{E121F64C-B8C4-0F40-B191-AE831CE89739}" name="Varighed _x000a_i år (inkl mobilisering + option på forlængelse)" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{7C4C5DD2-2A6C-C64E-A089-9781D5BE215F}" name="Oversigt over bodsbelagte emner" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{4DCDF279-AF71-2942-8851-EBDA7139034A}" name="Beskrivelse af og i givet fald hvordan bod/boderne maksimeres" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{973783A1-D420-0548-B15D-B8B32C2D8AFC}" name="Henvisning til hvor der er beskrevet i kontrakten" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{5453E985-0164-C543-B1C1-86C9A698144C}" name="Beskrivelse af beredskabet" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{53079FC0-F353-B34D-8CB6-2AF1A149C918}" name="Antal fejl, som leverandøren skal kunne håndtere på én gang." dataDxfId="42"/>
-    <tableColumn id="13" xr3:uid="{967BC99B-205D-954F-BC2C-26361136E5D6}" name="Antal arbejdshold og personer pr. hold, som leverandøren har pligt til at stille med." dataDxfId="41"/>
-    <tableColumn id="14" xr3:uid="{F50148C1-40FA-8F42-B043-85047598CF50}" name="Responstid" dataDxfId="40"/>
-    <tableColumn id="15" xr3:uid="{5557AA15-02A8-B841-A3D5-EEE9CB872D38}" name="Beskrivelse af boderne" dataDxfId="39"/>
-    <tableColumn id="16" xr3:uid="{FB4AA5E1-7370-D142-933F-6791C42A767B}" name="Henvisning til hvor der er beskrevet i kontrakten2" dataDxfId="38"/>
-    <tableColumn id="17" xr3:uid="{9E6E1A76-0349-D746-9348-CA49E95DDF88}" name="Krav til data registrering" dataDxfId="37"/>
-    <tableColumn id="18" xr3:uid="{C783E1BF-7F60-1E4E-AECA-63CB17E955C0}" name="Beskrevet fremgangsmåde omkring fejlretning" dataDxfId="36"/>
-    <tableColumn id="19" xr3:uid="{3E56ECBD-1029-E147-8B5C-A56461BD90B4}" name="Afrapporteringsfrekvens" dataDxfId="35"/>
-    <tableColumn id="20" xr3:uid="{4902EB2F-C24F-674F-BC17-F7E8AF445FEE}" name="Definitioner" dataDxfId="34"/>
-    <tableColumn id="21" xr3:uid="{D334E25E-52F1-5E48-9310-DB029EA34213}" name="GFS" dataDxfId="33"/>
-    <tableColumn id="22" xr3:uid="{4280621C-4231-2049-BEA6-D4AE8664BB63}" name="Kontraktansvarlig (leder)" dataDxfId="32"/>
-    <tableColumn id="23" xr3:uid="{F5D38B0B-F23F-9443-B5E5-41C863FFAFC4}" name="Column1" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{E619BD56-AE44-6E4E-8101-8116FAEFB42E}" name="Vedligeholdelsesforvalter" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{87A87DF0-814D-8D43-9129-4149CCF7622A}" name="SAP nummer" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{776EFCC3-20CB-9E4F-9740-1B00141C6B81}" name="Kontraktens titel" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{F6B1E8AC-E32C-8A47-BE7D-89927CA6D80E}" name="Leverandørnavn" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{2DBCDBCE-42CF-014F-B910-157DC783157C}" name="Geografisk område + Banenumre/TIB-strækning med responstid for den enkelte strækning" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{C11B38E0-A6FD-8D47-A62E-0E2EFEBC6C6D}" name="Ikraft-trædelse" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{E121F64C-B8C4-0F40-B191-AE831CE89739}" name="Varighed _x000a_i år (inkl mobilisering + option på forlængelse)" dataDxfId="52"/>
+    <tableColumn id="8" xr3:uid="{7C4C5DD2-2A6C-C64E-A089-9781D5BE215F}" name="Oversigt over bodsbelagte emner" dataDxfId="51"/>
+    <tableColumn id="9" xr3:uid="{4DCDF279-AF71-2942-8851-EBDA7139034A}" name="Beskrivelse af og i givet fald hvordan bod/boderne maksimeres" dataDxfId="50"/>
+    <tableColumn id="10" xr3:uid="{973783A1-D420-0548-B15D-B8B32C2D8AFC}" name="Henvisning til hvor der er beskrevet i kontrakten" dataDxfId="49"/>
+    <tableColumn id="11" xr3:uid="{5453E985-0164-C543-B1C1-86C9A698144C}" name="Beskrivelse af beredskabet" dataDxfId="48"/>
+    <tableColumn id="12" xr3:uid="{53079FC0-F353-B34D-8CB6-2AF1A149C918}" name="Antal fejl, som leverandøren skal kunne håndtere på én gang." dataDxfId="47"/>
+    <tableColumn id="13" xr3:uid="{967BC99B-205D-954F-BC2C-26361136E5D6}" name="Antal arbejdshold og personer pr. hold, som leverandøren har pligt til at stille med." dataDxfId="46"/>
+    <tableColumn id="14" xr3:uid="{F50148C1-40FA-8F42-B043-85047598CF50}" name="Responstid" dataDxfId="45"/>
+    <tableColumn id="15" xr3:uid="{5557AA15-02A8-B841-A3D5-EEE9CB872D38}" name="Beskrivelse af boderne" dataDxfId="44"/>
+    <tableColumn id="16" xr3:uid="{FB4AA5E1-7370-D142-933F-6791C42A767B}" name="Henvisning til hvor der er beskrevet i kontrakten2" dataDxfId="43"/>
+    <tableColumn id="17" xr3:uid="{9E6E1A76-0349-D746-9348-CA49E95DDF88}" name="Krav til data registrering" dataDxfId="42"/>
+    <tableColumn id="18" xr3:uid="{C783E1BF-7F60-1E4E-AECA-63CB17E955C0}" name="Beskrevet fremgangsmåde omkring fejlretning" dataDxfId="41"/>
+    <tableColumn id="19" xr3:uid="{3E56ECBD-1029-E147-8B5C-A56461BD90B4}" name="Afrapporteringsfrekvens" dataDxfId="40"/>
+    <tableColumn id="20" xr3:uid="{4902EB2F-C24F-674F-BC17-F7E8AF445FEE}" name="Definitioner" dataDxfId="39"/>
+    <tableColumn id="21" xr3:uid="{D334E25E-52F1-5E48-9310-DB029EA34213}" name="GFS" dataDxfId="38"/>
+    <tableColumn id="22" xr3:uid="{4280621C-4231-2049-BEA6-D4AE8664BB63}" name="Kontraktansvarlig (leder)" dataDxfId="37"/>
+    <tableColumn id="23" xr3:uid="{F5D38B0B-F23F-9443-B5E5-41C863FFAFC4}" name="Column1" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C8515571-1A4A-D843-A33A-6B6D44407D13}" name="Table8" displayName="Table8" ref="A1:J11" totalsRowShown="0" headerRowDxfId="98" dataDxfId="97">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C8515571-1A4A-D843-A33A-6B6D44407D13}" name="Table8" displayName="Table8" ref="A1:J11" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
   <autoFilter ref="A1:J11" xr:uid="{C8515571-1A4A-D843-A33A-6B6D44407D13}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{372BD9B7-8277-4F4B-BDCC-5371049B7BB5}" name="Afdeling " dataDxfId="96"/>
-    <tableColumn id="2" xr3:uid="{6AAC0E0C-B054-CF40-B2E1-347542DAA081}" name="Region" dataDxfId="95"/>
-    <tableColumn id="3" xr3:uid="{DAF2FDAB-3339-284E-9068-9A4EA18D8493}" name="Maks. Responstid i rådighedsvagten (minutter)" dataDxfId="94"/>
-    <tableColumn id="4" xr3:uid="{11D08DD4-7E81-0948-A6FB-0396846738ED}" name="Maks. Responstid i tjenestetiden (minutter" dataDxfId="93"/>
-    <tableColumn id="5" xr3:uid="{689550A2-7384-584F-AF93-65663881A974}" name="KPI-mål" dataDxfId="92"/>
-    <tableColumn id="6" xr3:uid="{86A454FD-6EB4-9D45-8222-55F8B0F0E5BE}" name="Beskrivelse af beredskabet" dataDxfId="91"/>
-    <tableColumn id="7" xr3:uid="{952C28F7-14E8-CD4F-B889-C1DA15AE457B}" name="Antal fejl som skal kunne håndteres på én gang " dataDxfId="90"/>
-    <tableColumn id="8" xr3:uid="{C8A1DA82-8135-BE42-A284-B9587153D1E8}" name="Antal arbejdshold og personer pr. hold, som der kan stilles med." dataDxfId="89"/>
-    <tableColumn id="9" xr3:uid="{517FF486-37E5-1541-B268-6757F8D1641C}" name="Krav til dataregistrering" dataDxfId="88"/>
-    <tableColumn id="10" xr3:uid="{DBD565CB-8682-394B-9B9D-00A4453B72B8}" name="Definitioner" dataDxfId="87"/>
+    <tableColumn id="1" xr3:uid="{372BD9B7-8277-4F4B-BDCC-5371049B7BB5}" name="Afdeling " dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{6AAC0E0C-B054-CF40-B2E1-347542DAA081}" name="Region" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{DAF2FDAB-3339-284E-9068-9A4EA18D8493}" name="Maks. Responstid i rådighedsvagten (minutter)" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{11D08DD4-7E81-0948-A6FB-0396846738ED}" name="Maks. Responstid i tjenestetiden (minutter" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{689550A2-7384-584F-AF93-65663881A974}" name="KPI-mål" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{86A454FD-6EB4-9D45-8222-55F8B0F0E5BE}" name="Beskrivelse af beredskabet" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{952C28F7-14E8-CD4F-B889-C1DA15AE457B}" name="Antal fejl som skal kunne håndteres på én gang " dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{C8A1DA82-8135-BE42-A284-B9587153D1E8}" name="Antal arbejdshold og personer pr. hold, som der kan stilles med." dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{517FF486-37E5-1541-B268-6757F8D1641C}" name="Krav til dataregistrering" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{DBD565CB-8682-394B-9B9D-00A4453B72B8}" name="Definitioner" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{783E0953-9616-BC41-9430-F3B53571FFEC}" name="Table1" displayName="Table1" ref="A1:AC97" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{783E0953-9616-BC41-9430-F3B53571FFEC}" name="Table1" displayName="Table1" ref="A1:AC97" totalsRowShown="0" headerRowDxfId="122" dataDxfId="121">
   <autoFilter ref="A1:AC97" xr:uid="{783E0953-9616-BC41-9430-F3B53571FFEC}"/>
   <tableColumns count="29">
-    <tableColumn id="1" xr3:uid="{5B279B2F-078D-0B48-8D5F-2B6DF47D0782}" name="Vedligeholdelsesforvalter" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{F95AB14E-F692-8E42-8BCF-C4B97CB34370}" name="Initialer " dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{679DC568-CC5E-B441-A4D7-E0AAC9BFEBD6}" name="SAP nummer" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{F53CAA04-ED2C-A447-A33E-63E30709812E}" name="Kontraktens titel" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{209A5E17-D876-7948-BD78-BE702896722A}" name="Leverandørnavn" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{41E0006D-F569-0A42-B6A5-FB581C472ACF}" name="Geografisk område" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{63F71911-D467-A54C-941C-70F0F06F8501}" name="Områdebeskrivelse" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{42B575E4-5DAB-D44D-A225-7B57A061962C}" name="Banenr. / TIB" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{6052AD68-6E8B-0C42-A435-831B98F86EF1}" name="Strækningsnummer" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{68EC9376-E4C0-9148-9E07-367633AC5183}" name="Fra" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{25030CC8-10FD-B345-B294-DCCF03A382FF}" name="Til" dataDxfId="20"/>
-    <tableColumn id="12" xr3:uid="{A574EDA6-932C-2042-9B8F-FC7082919569}" name="Strækningsbeskrivelse" dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{40C4323B-CBF3-CA44-B926-EF1AD83BF942}" name="Ikraft-trædelse" dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{0268D7C0-80A1-034B-9E3A-4FFE1B0975E2}" name="Varighed _x000a_i år (inkl mobilisering + option på forlængelse)" dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{613A8A79-8EF8-0442-8BC3-E32279B037CA}" name="Oversigt over bodsbelagte emner" dataDxfId="16"/>
-    <tableColumn id="16" xr3:uid="{E7A5A4AE-29B4-C44C-BD71-9BF1C9388757}" name="Beskrivelse af og i givet fald hvordan bod/boderne maksimeres" dataDxfId="15"/>
-    <tableColumn id="17" xr3:uid="{227BC6F0-AE6E-2444-A14D-4410AA7BCD28}" name="Henvisning til hvor der er beskrevet i kontrakten" dataDxfId="14"/>
-    <tableColumn id="18" xr3:uid="{50352A57-6845-044D-B7ED-E58B77A55437}" name="Beskrivelse af beredskabet" dataDxfId="13"/>
-    <tableColumn id="19" xr3:uid="{C825C42B-5E1F-BB48-A634-B9A58A6B51CE}" name="Antal fejl, som leverandøren skal kunne håndtere på én gang." dataDxfId="12"/>
-    <tableColumn id="20" xr3:uid="{D7883B66-6BF8-5248-AEF0-480921D35730}" name="Antal arbejdshold og personer pr. hold, som leverandøren har pligt til at stille med." dataDxfId="11"/>
-    <tableColumn id="21" xr3:uid="{D9F217B2-D76B-614F-89A2-995AA1CC65BA}" name="Responstid" dataDxfId="10"/>
-    <tableColumn id="22" xr3:uid="{1A51B275-CC57-8144-A837-9A1B3698A3E3}" name="Beskrivelse af boderne" dataDxfId="9"/>
-    <tableColumn id="23" xr3:uid="{AD97A15E-D5EE-854C-B547-5F5F4C362833}" name="Henvisning til hvor der er beskrevet i kontrakten2" dataDxfId="8"/>
-    <tableColumn id="24" xr3:uid="{7A4C7F8F-1CD3-5E47-82DD-391D30FD0872}" name="Krav til data registrering" dataDxfId="7"/>
-    <tableColumn id="25" xr3:uid="{06CD6733-0485-7D4F-906A-32C1DD5BF94C}" name="Beskrevet fremgangsmåde ved fejlretning" dataDxfId="6"/>
-    <tableColumn id="26" xr3:uid="{4A4F9ED6-86B5-914A-8C1E-9BC9C36FCFDA}" name="Afrapporteringsfrekvens" dataDxfId="5"/>
-    <tableColumn id="27" xr3:uid="{B9DC52B0-A93A-704B-A81F-091056BCF004}" name="Definitioner" dataDxfId="4"/>
-    <tableColumn id="28" xr3:uid="{DE5D79D7-8CF2-CF43-B3C2-4C0F74E0029B}" name="GFS" dataDxfId="3"/>
-    <tableColumn id="29" xr3:uid="{9CDC489C-79EE-674C-B66A-60451F0375FF}" name="Kontraktansvarlig (leder)" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{5B279B2F-078D-0B48-8D5F-2B6DF47D0782}" name="Vedligeholdelsesforvalter" dataDxfId="120"/>
+    <tableColumn id="2" xr3:uid="{F95AB14E-F692-8E42-8BCF-C4B97CB34370}" name="Initialer " dataDxfId="119"/>
+    <tableColumn id="3" xr3:uid="{679DC568-CC5E-B441-A4D7-E0AAC9BFEBD6}" name="SAP nummer" dataDxfId="118"/>
+    <tableColumn id="4" xr3:uid="{F53CAA04-ED2C-A447-A33E-63E30709812E}" name="Kontraktens titel" dataDxfId="117"/>
+    <tableColumn id="5" xr3:uid="{209A5E17-D876-7948-BD78-BE702896722A}" name="Leverandørnavn" dataDxfId="116"/>
+    <tableColumn id="6" xr3:uid="{41E0006D-F569-0A42-B6A5-FB581C472ACF}" name="Geografisk område" dataDxfId="115"/>
+    <tableColumn id="7" xr3:uid="{63F71911-D467-A54C-941C-70F0F06F8501}" name="Områdebeskrivelse" dataDxfId="114"/>
+    <tableColumn id="8" xr3:uid="{42B575E4-5DAB-D44D-A225-7B57A061962C}" name="Banenr. / TIB" dataDxfId="113"/>
+    <tableColumn id="9" xr3:uid="{6052AD68-6E8B-0C42-A435-831B98F86EF1}" name="Strækningsnummer" dataDxfId="112"/>
+    <tableColumn id="10" xr3:uid="{68EC9376-E4C0-9148-9E07-367633AC5183}" name="Fra" dataDxfId="111"/>
+    <tableColumn id="11" xr3:uid="{25030CC8-10FD-B345-B294-DCCF03A382FF}" name="Til" dataDxfId="110"/>
+    <tableColumn id="12" xr3:uid="{A574EDA6-932C-2042-9B8F-FC7082919569}" name="Strækningsbeskrivelse" dataDxfId="109"/>
+    <tableColumn id="13" xr3:uid="{40C4323B-CBF3-CA44-B926-EF1AD83BF942}" name="Ikraft-trædelse" dataDxfId="108"/>
+    <tableColumn id="14" xr3:uid="{0268D7C0-80A1-034B-9E3A-4FFE1B0975E2}" name="Varighed _x000a_i år (inkl mobilisering + option på forlængelse)" dataDxfId="107"/>
+    <tableColumn id="15" xr3:uid="{613A8A79-8EF8-0442-8BC3-E32279B037CA}" name="Oversigt over bodsbelagte emner" dataDxfId="106"/>
+    <tableColumn id="16" xr3:uid="{E7A5A4AE-29B4-C44C-BD71-9BF1C9388757}" name="Beskrivelse af og i givet fald hvordan bod/boderne maksimeres" dataDxfId="105"/>
+    <tableColumn id="17" xr3:uid="{227BC6F0-AE6E-2444-A14D-4410AA7BCD28}" name="Henvisning til hvor der er beskrevet i kontrakten" dataDxfId="104"/>
+    <tableColumn id="18" xr3:uid="{50352A57-6845-044D-B7ED-E58B77A55437}" name="Beskrivelse af beredskabet" dataDxfId="103"/>
+    <tableColumn id="19" xr3:uid="{C825C42B-5E1F-BB48-A634-B9A58A6B51CE}" name="Antal fejl, som leverandøren skal kunne håndtere på én gang." dataDxfId="102"/>
+    <tableColumn id="20" xr3:uid="{D7883B66-6BF8-5248-AEF0-480921D35730}" name="Antal arbejdshold og personer pr. hold, som leverandøren har pligt til at stille med." dataDxfId="101"/>
+    <tableColumn id="21" xr3:uid="{D9F217B2-D76B-614F-89A2-995AA1CC65BA}" name="Responstid" dataDxfId="100"/>
+    <tableColumn id="22" xr3:uid="{1A51B275-CC57-8144-A837-9A1B3698A3E3}" name="Beskrivelse af boderne" dataDxfId="99"/>
+    <tableColumn id="23" xr3:uid="{AD97A15E-D5EE-854C-B547-5F5F4C362833}" name="Henvisning til hvor der er beskrevet i kontrakten2" dataDxfId="98"/>
+    <tableColumn id="24" xr3:uid="{7A4C7F8F-1CD3-5E47-82DD-391D30FD0872}" name="Krav til data registrering" dataDxfId="97"/>
+    <tableColumn id="25" xr3:uid="{06CD6733-0485-7D4F-906A-32C1DD5BF94C}" name="Beskrevet fremgangsmåde ved fejlretning" dataDxfId="96"/>
+    <tableColumn id="26" xr3:uid="{4A4F9ED6-86B5-914A-8C1E-9BC9C36FCFDA}" name="Afrapporteringsfrekvens" dataDxfId="95"/>
+    <tableColumn id="27" xr3:uid="{B9DC52B0-A93A-704B-A81F-091056BCF004}" name="Definitioner" dataDxfId="94"/>
+    <tableColumn id="28" xr3:uid="{DE5D79D7-8CF2-CF43-B3C2-4C0F74E0029B}" name="GFS" dataDxfId="93"/>
+    <tableColumn id="29" xr3:uid="{9CDC489C-79EE-674C-B66A-60451F0375FF}" name="Kontraktansvarlig (leder)" dataDxfId="92"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{81578B11-51B0-6544-86F9-382A4F91D85B}" name="Table2" displayName="Table2" ref="A1:V12" totalsRowShown="0" headerRowDxfId="3" dataDxfId="4">
+  <autoFilter ref="A1:V12" xr:uid="{81578B11-51B0-6544-86F9-382A4F91D85B}"/>
+  <tableColumns count="22">
+    <tableColumn id="1" xr3:uid="{F2D534E6-0C4E-E34B-BD6B-71491C2A092B}" name="Vedligeholdsesforvalter" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{2470380C-E386-0249-BC5F-50E39041C260}" name="SAP nummer" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{F95AFBD3-E1DF-F241-A158-231DE83EF9DD}" name="Kontraktens titel" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{E3029144-9D16-D543-B4D6-5AAF59A6478C}" name="Leverandørnavn" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{F82DA6CF-3726-654A-90F5-E3A2E6A4E0EA}" name="Geografisk område + Banenumre / TIB strækning med responstid for enkelt strækning" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{FA6EFA2D-C2F6-F849-A745-6FE7618A3D15}" name="Ikraft-trædelse" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{D67CB641-42A7-E749-B135-2FAC1D6D0A8D}" name="Varighed i år (inkl. mobilisering + option på forlængelse)" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{C3E7F6BC-50B3-EF43-8143-AF786BF081CF}" name="Oversigt over bodsbelagte emner" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{387D4374-ED0D-0844-B089-68F780D20AB8}" name="Beskrivelse af og i givet fald hvordan bod/boderne maksimeres" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{58650D8A-2BE6-CF45-8FB1-23E3AEA19A5B}" name="Henvisning til hvor det er beskrevet i kontrakten" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{50F93262-253F-6249-A40F-E1FDA907DA9D}" name="Beskrivelse af beredskabet " dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{E51B5EE8-2703-E64D-BAE2-645E8B72BAC4}" name="Antal fejl, som leverandøren skal kunne håndtere på én gang" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{F2FFCA46-177F-F64B-8D66-FB601EE263A2}" name="Antal arbejdshold og personer pr. hold som leverandøren har pligt til at stille med" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{150C5C49-227E-7C4C-B56D-5EC22821DDCB}" name="Responstid" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{24157B28-9AB9-5249-BDE1-73C5B123FCC1}" name="Beskrivelse af boderne" dataDxfId="9"/>
+    <tableColumn id="16" xr3:uid="{282F2E90-C731-174E-9679-5766AE023961}" name="Henvisning til hvor det er beskrevet i kontrakten2" dataDxfId="8"/>
+    <tableColumn id="17" xr3:uid="{E2FEF229-A16A-DC40-86DB-27049046923E}" name="Krav til data registrering" dataDxfId="7"/>
+    <tableColumn id="18" xr3:uid="{6BD9A198-E871-574E-88EB-5153101F5596}" name="Beskrevet fremgangsmåde omkring fejlretning" dataDxfId="6"/>
+    <tableColumn id="19" xr3:uid="{92ACB7D1-E88B-D846-A57C-0509C6259BA8}" name="Afrapporteringsfrekvens leverandør" dataDxfId="5"/>
+    <tableColumn id="20" xr3:uid="{78A382D7-BE30-0A45-845C-C60A9A3924E9}" name="Definitioner " dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{3215051C-9921-1741-807D-5022D4E01794}" name="GFS" dataDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{6B80E667-212B-C04F-9DE2-786BE9D42AE5}" name="Kontraktansvarlig (leder)" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -17642,4 +19005,798 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89CDAB9F-0640-DB49-A658-E047C77B5D71}">
+  <dimension ref="A1:V12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.5" style="22" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="38.6640625" customWidth="1"/>
+    <col min="7" max="7" width="28.1640625" customWidth="1"/>
+    <col min="8" max="8" width="25.33203125" customWidth="1"/>
+    <col min="9" max="9" width="30.1640625" customWidth="1"/>
+    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="11" max="11" width="33.5" customWidth="1"/>
+    <col min="12" max="12" width="23.33203125" customWidth="1"/>
+    <col min="13" max="13" width="24.5" customWidth="1"/>
+    <col min="14" max="14" width="22.5" customWidth="1"/>
+    <col min="15" max="15" width="22.6640625" customWidth="1"/>
+    <col min="16" max="16" width="11.83203125" customWidth="1"/>
+    <col min="17" max="17" width="30.83203125" customWidth="1"/>
+    <col min="18" max="18" width="49.83203125" customWidth="1"/>
+    <col min="19" max="19" width="22.5" customWidth="1"/>
+    <col min="20" max="20" width="20.33203125" customWidth="1"/>
+    <col min="21" max="21" width="23.1640625" customWidth="1"/>
+    <col min="22" max="22" width="24.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" s="53" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+      <c r="A1" s="52" t="s">
+        <v>455</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="52" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="52" t="s">
+        <v>465</v>
+      </c>
+      <c r="F1" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="52" t="s">
+        <v>477</v>
+      </c>
+      <c r="H1" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="52" t="s">
+        <v>314</v>
+      </c>
+      <c r="K1" s="52" t="s">
+        <v>480</v>
+      </c>
+      <c r="L1" s="52" t="s">
+        <v>481</v>
+      </c>
+      <c r="M1" s="52" t="s">
+        <v>482</v>
+      </c>
+      <c r="N1" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="52" t="s">
+        <v>483</v>
+      </c>
+      <c r="Q1" s="52" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="52" t="s">
+        <v>485</v>
+      </c>
+      <c r="T1" s="52" t="s">
+        <v>319</v>
+      </c>
+      <c r="U1" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="54" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="184" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="B2" s="24">
+        <v>1720000104</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>466</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>478</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" s="55" t="s">
+        <v>486</v>
+      </c>
+      <c r="U2" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A3" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="B3" s="24">
+        <v>1720000105</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>467</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>479</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="R3" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" s="55" t="s">
+        <v>486</v>
+      </c>
+      <c r="U3" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="V3" s="56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A4" s="23" t="s">
+        <v>457</v>
+      </c>
+      <c r="B4" s="24">
+        <v>1720000106</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="E4" s="37" t="s">
+        <v>468</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="O4" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="R4" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4" s="55" t="s">
+        <v>486</v>
+      </c>
+      <c r="U4" s="32" t="s">
+        <v>487</v>
+      </c>
+      <c r="V4" s="56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A5" s="23" t="s">
+        <v>457</v>
+      </c>
+      <c r="B5" s="24">
+        <v>1720000107</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>462</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>469</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="R5" s="32" t="s">
+        <v>484</v>
+      </c>
+      <c r="S5" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="T5" s="55" t="s">
+        <v>486</v>
+      </c>
+      <c r="U5" s="32" t="s">
+        <v>488</v>
+      </c>
+      <c r="V5" s="56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="240" x14ac:dyDescent="0.2">
+      <c r="A6" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="B6" s="24">
+        <v>1820005380</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="M6" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q6" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="R6" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="S6" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="T6" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="U6" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="V6" s="56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="225" x14ac:dyDescent="0.2">
+      <c r="A7" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="B7" s="24">
+        <v>1820005381</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>471</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="M7" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="N7" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="T7" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="U7" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="V7" s="56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A8" s="23" t="s">
+        <v>459</v>
+      </c>
+      <c r="B8" s="24">
+        <v>1720000368</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="O8" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="P8" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="T8" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="U8" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="V8" s="56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A9" s="23" t="s">
+        <v>459</v>
+      </c>
+      <c r="B9" s="24">
+        <v>1720000369</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="O9" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="P9" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="T9" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="U9" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="V9" s="56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="150" x14ac:dyDescent="0.2">
+      <c r="A10" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="B10" s="24">
+        <v>1820006668</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="M10" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="N10" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="O10" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="P10" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="T10" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="U10" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="V10" s="56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A11" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="B11" s="24">
+        <v>1820006669</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>475</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="J11" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="M11" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="N11" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="O11" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="P11" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="T11" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="U11" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="V11" s="56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="48" x14ac:dyDescent="0.2">
+      <c r="A12" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="B12" s="24">
+        <v>1720000460</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="48" t="s">
+        <v>464</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>476</v>
+      </c>
+      <c r="F12" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="48">
+        <v>5</v>
+      </c>
+      <c r="H12" s="48"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="51"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="V12" s="56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Oversigt over kontrakter på Spor Strøm forst og Sikring.xlsx
+++ b/Oversigt over kontrakter på Spor Strøm forst og Sikring.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeppebondebakkensen/Library/Mobile Documents/com~apple~CloudDocs/Test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SKSV\Downloads\Stineprojekt-main\Stineprojekt-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AFC4EB5-849B-094F-A7A3-ACC298FA7330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656E7B51-5C86-4F0C-BCF8-E136F83D75A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="510" yWindow="1590" windowWidth="16860" windowHeight="11100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Strøm og Materiel" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5841" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5841" uniqueCount="488">
   <si>
     <t>Vedligeholdelsesforvalter</t>
   </si>
@@ -1737,6 +1737,15 @@
   </si>
   <si>
     <t>TIB 1</t>
+  </si>
+  <si>
+    <t>Indeles efter 5 kategorier (X,Y,Z,WN): 
+Fatale fejl: X: 2,5t, Y: 3t, Z: 24t, W: 2DG, N: 1mdr.
+Forstyrrende fej:Y: 8T, Z: 24T, W: 2DG: N: 1 mdr. 
+Genrende Fejl: Y: 1 DG, N: 7DG</t>
+  </si>
+  <si>
+    <t>Vedligehold af kørestrøm Vest (Fordelingsstationer)</t>
   </si>
 </sst>
 </file>
@@ -1772,8 +1781,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2114,9 +2132,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC103"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2205,7 +2223,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -2294,7 +2312,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -2383,7 +2401,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -2472,7 +2490,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -2561,7 +2579,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -2650,7 +2668,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -2739,7 +2757,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -2828,7 +2846,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -2917,7 +2935,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -3006,7 +3024,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -3095,7 +3113,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -3184,7 +3202,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -3273,7 +3291,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -3362,7 +3380,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -3451,7 +3469,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -3540,7 +3558,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -3629,7 +3647,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -3718,7 +3736,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -3807,7 +3825,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -3896,7 +3914,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -3985,7 +4003,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -4074,7 +4092,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -4163,7 +4181,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -4252,7 +4270,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -4341,7 +4359,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -4430,7 +4448,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -4519,7 +4537,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -4608,7 +4626,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -4697,7 +4715,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>142</v>
       </c>
@@ -4786,7 +4804,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>142</v>
       </c>
@@ -4875,7 +4893,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>142</v>
       </c>
@@ -4964,7 +4982,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>142</v>
       </c>
@@ -5053,7 +5071,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>142</v>
       </c>
@@ -5142,7 +5160,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>142</v>
       </c>
@@ -5231,7 +5249,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>142</v>
       </c>
@@ -5320,7 +5338,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>142</v>
       </c>
@@ -5409,7 +5427,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>142</v>
       </c>
@@ -5498,7 +5516,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>142</v>
       </c>
@@ -5587,7 +5605,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>142</v>
       </c>
@@ -5676,7 +5694,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>142</v>
       </c>
@@ -5765,7 +5783,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>142</v>
       </c>
@@ -5854,7 +5872,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>142</v>
       </c>
@@ -5943,7 +5961,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>142</v>
       </c>
@@ -6032,7 +6050,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>142</v>
       </c>
@@ -6121,7 +6139,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>142</v>
       </c>
@@ -6210,7 +6228,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>142</v>
       </c>
@@ -6299,7 +6317,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>142</v>
       </c>
@@ -6388,7 +6406,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>142</v>
       </c>
@@ -6477,7 +6495,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>142</v>
       </c>
@@ -6566,7 +6584,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>224</v>
       </c>
@@ -6655,7 +6673,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>224</v>
       </c>
@@ -6744,7 +6762,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>224</v>
       </c>
@@ -6833,7 +6851,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>224</v>
       </c>
@@ -6922,7 +6940,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>224</v>
       </c>
@@ -7011,7 +7029,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>224</v>
       </c>
@@ -7100,7 +7118,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>224</v>
       </c>
@@ -7189,7 +7207,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>224</v>
       </c>
@@ -7278,7 +7296,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>224</v>
       </c>
@@ -7367,7 +7385,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>224</v>
       </c>
@@ -7456,7 +7474,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>224</v>
       </c>
@@ -7517,8 +7535,8 @@
       <c r="T61" t="s">
         <v>236</v>
       </c>
-      <c r="U61" t="s">
-        <v>237</v>
+      <c r="U61" s="1" t="s">
+        <v>486</v>
       </c>
       <c r="V61" t="s">
         <v>34</v>
@@ -7545,7 +7563,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>224</v>
       </c>
@@ -7634,7 +7652,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>224</v>
       </c>
@@ -7723,7 +7741,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>224</v>
       </c>
@@ -7734,7 +7752,7 @@
         <v>1820005381</v>
       </c>
       <c r="D64" t="s">
-        <v>261</v>
+        <v>487</v>
       </c>
       <c r="E64" t="s">
         <v>145</v>
@@ -7812,7 +7830,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>224</v>
       </c>
@@ -7823,7 +7841,7 @@
         <v>1820005381</v>
       </c>
       <c r="D65" t="s">
-        <v>261</v>
+        <v>487</v>
       </c>
       <c r="E65" t="s">
         <v>145</v>
@@ -7901,96 +7919,96 @@
         <v>243</v>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+    <row r="66" spans="1:29" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="2">
         <v>1820005381</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="G66" t="s">
-        <v>34</v>
-      </c>
-      <c r="H66" t="s">
+      <c r="G66" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H66" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I66" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J66" t="s">
+      <c r="J66" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="K66" t="s">
+      <c r="K66" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L66" t="s">
+      <c r="L66" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="M66" t="s">
+      <c r="M66" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="N66" t="s">
+      <c r="N66" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="O66" t="s">
+      <c r="O66" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="P66" t="s">
+      <c r="P66" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="Q66" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="R66" t="s">
+      <c r="R66" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="S66" t="s">
+      <c r="S66" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="T66" t="s">
+      <c r="T66" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="U66" t="s">
-        <v>237</v>
-      </c>
-      <c r="V66" t="s">
-        <v>34</v>
-      </c>
-      <c r="W66" t="s">
+      <c r="U66" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W66" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="X66" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z66" t="s">
+      <c r="X66" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y66" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z66" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="AA66" t="s">
+      <c r="AA66" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="AB66" t="s">
+      <c r="AB66" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AC66" t="s">
+      <c r="AC66" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>224</v>
       </c>
@@ -8079,7 +8097,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>224</v>
       </c>
@@ -8168,7 +8186,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>224</v>
       </c>
@@ -8257,7 +8275,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>268</v>
       </c>
@@ -8346,7 +8364,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>268</v>
       </c>
@@ -8435,7 +8453,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>268</v>
       </c>
@@ -8524,7 +8542,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>268</v>
       </c>
@@ -8613,7 +8631,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>268</v>
       </c>
@@ -8702,7 +8720,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>268</v>
       </c>
@@ -8791,7 +8809,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>268</v>
       </c>
@@ -8880,7 +8898,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>268</v>
       </c>
@@ -8969,7 +8987,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>268</v>
       </c>
@@ -9058,7 +9076,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>268</v>
       </c>
@@ -9147,7 +9165,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>268</v>
       </c>
@@ -9236,7 +9254,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>268</v>
       </c>
@@ -9325,7 +9343,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>268</v>
       </c>
@@ -9414,7 +9432,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>268</v>
       </c>
@@ -9503,7 +9521,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>268</v>
       </c>
@@ -9592,7 +9610,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>268</v>
       </c>
@@ -9681,7 +9699,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>268</v>
       </c>
@@ -9770,7 +9788,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>286</v>
       </c>
@@ -9859,7 +9877,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>286</v>
       </c>
@@ -9948,7 +9966,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>286</v>
       </c>
@@ -10037,7 +10055,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>286</v>
       </c>
@@ -10126,7 +10144,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>286</v>
       </c>
@@ -10215,7 +10233,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>286</v>
       </c>
@@ -10304,7 +10322,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>286</v>
       </c>
@@ -10393,7 +10411,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>286</v>
       </c>
@@ -10482,7 +10500,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>286</v>
       </c>
@@ -10571,7 +10589,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>286</v>
       </c>
@@ -10660,7 +10678,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>286</v>
       </c>
@@ -10749,7 +10767,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>286</v>
       </c>
@@ -10838,7 +10856,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>286</v>
       </c>
@@ -10927,7 +10945,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>315</v>
       </c>
@@ -11016,7 +11034,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>34</v>
       </c>
@@ -11105,7 +11123,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>34</v>
       </c>
@@ -11194,7 +11212,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>34</v>
       </c>
@@ -11286,7 +11304,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AC103" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AC60 A62:AC63 A61:T61 V61:AC61 A67:AC103 A66:B66 V66:AC66 A65:C65 A64:C64 E64:AC64 E65:AC65 F66:T66" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -11294,32 +11312,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="107.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="107.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="95" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="138.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="47.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="47.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="54" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="255.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="52.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="243.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="255.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="41.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="255.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="52.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="243.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="255.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="41.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="39.625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="21" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11387,7 +11405,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>325</v>
       </c>
@@ -11434,7 +11452,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>1820007057</v>
       </c>
@@ -11481,7 +11499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1820009599</v>
       </c>
@@ -11528,7 +11546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1820008546</v>
       </c>
@@ -11575,7 +11593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1820009889</v>
       </c>
@@ -11622,7 +11640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1820006477</v>
       </c>
@@ -11669,7 +11687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1820001663</v>
       </c>
@@ -11716,7 +11734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1800001122</v>
       </c>
@@ -11763,7 +11781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1800007494</v>
       </c>
@@ -11810,7 +11828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1800001120</v>
       </c>
@@ -11857,7 +11875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>1800006244</v>
       </c>
@@ -11915,21 +11933,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="51" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="255.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="255.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="100" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="59.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="86.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="59.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="86.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>383</v>
       </c>
@@ -11961,7 +11979,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>391</v>
       </c>
@@ -11993,7 +12011,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>391</v>
       </c>
@@ -12025,7 +12043,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>391</v>
       </c>
@@ -12057,7 +12075,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>402</v>
       </c>
@@ -12089,7 +12107,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>391</v>
       </c>
@@ -12121,7 +12139,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>407</v>
       </c>
@@ -12153,7 +12171,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>407</v>
       </c>
@@ -12185,7 +12203,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>407</v>
       </c>
@@ -12217,7 +12235,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>407</v>
       </c>
@@ -12249,7 +12267,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>414</v>
       </c>
@@ -12292,13 +12310,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AC97"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12387,7 +12405,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>416</v>
       </c>
@@ -12473,7 +12491,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>416</v>
       </c>
@@ -12559,7 +12577,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>416</v>
       </c>
@@ -12645,7 +12663,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>416</v>
       </c>
@@ -12731,7 +12749,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>416</v>
       </c>
@@ -12817,7 +12835,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>416</v>
       </c>
@@ -12903,7 +12921,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>416</v>
       </c>
@@ -12989,7 +13007,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>416</v>
       </c>
@@ -13075,7 +13093,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>416</v>
       </c>
@@ -13161,7 +13179,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>416</v>
       </c>
@@ -13247,7 +13265,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>416</v>
       </c>
@@ -13333,7 +13351,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>416</v>
       </c>
@@ -13419,7 +13437,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>416</v>
       </c>
@@ -13505,7 +13523,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>416</v>
       </c>
@@ -13591,7 +13609,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>416</v>
       </c>
@@ -13677,7 +13695,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>416</v>
       </c>
@@ -13763,7 +13781,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>416</v>
       </c>
@@ -13849,7 +13867,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>416</v>
       </c>
@@ -13935,7 +13953,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>416</v>
       </c>
@@ -14021,7 +14039,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>416</v>
       </c>
@@ -14107,7 +14125,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>416</v>
       </c>
@@ -14193,7 +14211,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>416</v>
       </c>
@@ -14279,7 +14297,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>416</v>
       </c>
@@ -14365,7 +14383,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>416</v>
       </c>
@@ -14451,7 +14469,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>416</v>
       </c>
@@ -14537,7 +14555,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>416</v>
       </c>
@@ -14623,7 +14641,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>416</v>
       </c>
@@ -14709,7 +14727,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>416</v>
       </c>
@@ -14795,7 +14813,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>416</v>
       </c>
@@ -14881,7 +14899,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>416</v>
       </c>
@@ -14967,7 +14985,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>416</v>
       </c>
@@ -15053,7 +15071,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>416</v>
       </c>
@@ -15139,7 +15157,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>436</v>
       </c>
@@ -15225,7 +15243,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>436</v>
       </c>
@@ -15311,7 +15329,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>436</v>
       </c>
@@ -15397,7 +15415,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>436</v>
       </c>
@@ -15483,7 +15501,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>436</v>
       </c>
@@ -15569,7 +15587,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>436</v>
       </c>
@@ -15655,7 +15673,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>436</v>
       </c>
@@ -15741,7 +15759,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>436</v>
       </c>
@@ -15827,7 +15845,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>436</v>
       </c>
@@ -15913,7 +15931,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>436</v>
       </c>
@@ -15999,7 +16017,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>436</v>
       </c>
@@ -16085,7 +16103,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>436</v>
       </c>
@@ -16171,7 +16189,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>436</v>
       </c>
@@ -16257,7 +16275,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>436</v>
       </c>
@@ -16343,7 +16361,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>436</v>
       </c>
@@ -16429,7 +16447,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>436</v>
       </c>
@@ -16515,7 +16533,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>436</v>
       </c>
@@ -16601,7 +16619,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>436</v>
       </c>
@@ -16687,7 +16705,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>436</v>
       </c>
@@ -16773,7 +16791,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>436</v>
       </c>
@@ -16859,7 +16877,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>436</v>
       </c>
@@ -16945,7 +16963,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>436</v>
       </c>
@@ -17031,7 +17049,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>436</v>
       </c>
@@ -17117,7 +17135,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>436</v>
       </c>
@@ -17203,7 +17221,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>436</v>
       </c>
@@ -17289,7 +17307,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>436</v>
       </c>
@@ -17375,7 +17393,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>436</v>
       </c>
@@ -17461,7 +17479,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>436</v>
       </c>
@@ -17547,7 +17565,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>436</v>
       </c>
@@ -17633,7 +17651,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>436</v>
       </c>
@@ -17719,7 +17737,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>436</v>
       </c>
@@ -17805,7 +17823,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>436</v>
       </c>
@@ -17891,7 +17909,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>34</v>
       </c>
@@ -17977,7 +17995,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>34</v>
       </c>
@@ -18063,7 +18081,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>34</v>
       </c>
@@ -18149,7 +18167,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>34</v>
       </c>
@@ -18235,7 +18253,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>34</v>
       </c>
@@ -18321,7 +18339,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>34</v>
       </c>
@@ -18407,7 +18425,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>34</v>
       </c>
@@ -18493,7 +18511,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>34</v>
       </c>
@@ -18579,7 +18597,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>34</v>
       </c>
@@ -18665,7 +18683,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>34</v>
       </c>
@@ -18751,7 +18769,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>34</v>
       </c>
@@ -18837,7 +18855,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>34</v>
       </c>
@@ -18923,7 +18941,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>34</v>
       </c>
@@ -19009,7 +19027,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>34</v>
       </c>
@@ -19095,7 +19113,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>34</v>
       </c>
@@ -19181,7 +19199,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>34</v>
       </c>
@@ -19267,7 +19285,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>34</v>
       </c>
@@ -19353,7 +19371,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>34</v>
       </c>
@@ -19439,7 +19457,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>34</v>
       </c>
@@ -19525,7 +19543,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>34</v>
       </c>
@@ -19611,7 +19629,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>34</v>
       </c>
@@ -19697,7 +19715,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>34</v>
       </c>
@@ -19783,7 +19801,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>34</v>
       </c>
@@ -19869,7 +19887,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>34</v>
       </c>
@@ -19955,7 +19973,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>34</v>
       </c>
@@ -20041,7 +20059,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>34</v>
       </c>
@@ -20127,7 +20145,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>34</v>
       </c>
@@ -20213,7 +20231,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>34</v>
       </c>
@@ -20299,7 +20317,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>34</v>
       </c>
@@ -20385,7 +20403,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>34</v>
       </c>
@@ -20471,7 +20489,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>34</v>
       </c>
@@ -20557,7 +20575,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>34</v>
       </c>
@@ -20654,9 +20672,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:V12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>453</v>
       </c>
@@ -20724,7 +20742,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>461</v>
       </c>
@@ -20792,7 +20810,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>461</v>
       </c>
@@ -20860,7 +20878,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>465</v>
       </c>
@@ -20928,7 +20946,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>465</v>
       </c>
@@ -20996,7 +21014,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>474</v>
       </c>
@@ -21061,7 +21079,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>474</v>
       </c>
@@ -21120,7 +21138,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>477</v>
       </c>
@@ -21176,7 +21194,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>477</v>
       </c>
@@ -21232,7 +21250,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>480</v>
       </c>
@@ -21294,7 +21312,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>480</v>
       </c>
@@ -21356,7 +21374,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>474</v>
       </c>
